--- a/experiments/completed_experiments/aminoadipate_202504291411/protocol/hamilton/pipetting_layout.xlsx
+++ b/experiments/completed_experiments/aminoadipate_202504291411/protocol/hamilton/pipetting_layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/glutamate_202504291411/protocol/hamilton/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/completed_experiments/aminoadipate_202504291411/protocol/hamilton/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_55B93094595CE00E62355476585DCE3A8746CCB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A6B415-75CD-9647-B176-11CCD1036226}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_55B93094595CE00E62355476585DCE3A8746CCB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B473210-037D-9243-881C-021C91F5DC3B}"/>
   <bookViews>
-    <workbookView xWindow="-35840" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1720" windowWidth="51200" windowHeight="27080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,6 +483,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,6 +778,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="108" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
